--- a/LubanTmpl/Datas/localization.xlsx
+++ b/LubanTmpl/Datas/localization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30313"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30319"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Thirds\XIHFrameWork\LubanTmpl\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863E5E41-7076-4B59-84DF-D622787D8577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E80E5B6-0AA4-479C-9627-45C296AEB926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="0" windowWidth="28830" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1095" yWindow="30" windowWidth="28830" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -108,12 +108,6 @@
   </si>
   <si>
     <t>SFX</t>
-  </si>
-  <si>
-    <t>声音</t>
-  </si>
-  <si>
-    <t>Sound</t>
   </si>
   <si>
     <t>震动</t>
@@ -694,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -782,7 +776,7 @@
         <v>12</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -879,17 +873,6 @@
       </c>
       <c r="D16" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" s="6">
-        <v>790005</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
